--- a/processed_ruby_restored_xlsx/sc246_みるく８：牛乳風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc246_みるく８：牛乳風呂.ss.xlsx
@@ -514,8 +514,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>I always think about it, but since I'm making everyone
-feel refreshed, I can't slack off.</t>
+          <t>I always think about it, but since I'm making
+everyone feel refreshed, I can't slack off.</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -745,8 +745,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>「The bath's ready. All that's left is to add this bath
-salt.」</t>
+          <t>「The bath's ready. All that's left is to add this
+bath salt.」</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1813,8 +1813,8 @@
       <c r="B89" s="1" t="inlineStr">
         <is>
           <t>I hurriedly changed the subject and said we should go
-in together, and Miru-chan answered on the spur of the
-moment too.</t>
+in together, and Miru-chan answered on the spur of
+the moment too.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2010,8 +2010,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>I quickly stripped in the changing room, gave myself a
-perfunctory splash of water, invited Miru-chan, and
+          <t>I quickly stripped in the changing room, gave myself
+a perfunctory splash of water, invited Miru-chan, and
 immediately got into the tub.</t>
         </is>
       </c>
@@ -2167,9 +2167,9 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>I think she’s laughing to cover her embarrassment, but
-even so she’s leaning against me with her back against
-mine.</t>
+          <t>I think she’s laughing to cover her embarrassment,
+but even so she’s leaning against me with her back
+against mine.</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2384,8 +2384,8 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>If you tease her at a time like that, you might end up
-making her angry.</t>
+          <t>If you tease her at a time like that, you might end
+up making her angry.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2567,8 +2567,8 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Feeling the water cling to my arm, I ran my hand along
-Miru-chan's arm.</t>
+          <t>Feeling the water cling to my arm, I ran my hand
+along Miru-chan's arm.</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2873,8 +2873,8 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>She hugged me apologetically, and Miru-chan's momentum
-eased.</t>
+          <t>She hugged me apologetically, and Miru-chan's
+momentum eased.</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2935,7 +2935,8 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>I tried to peek at Miru-chan's face over her shoulder.</t>
+          <t>I tried to peek at Miru-chan's face over her
+shoulder.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3180,8 +3181,8 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>I straightened my back and acted like I wasn't looking
-anymore.</t>
+          <t>I straightened my back and acted like I wasn't
+looking anymore.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3531,8 +3532,8 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>She should already get it, but I guess she still wants
-to pretend she doesn't.</t>
+          <t>She should already get it, but I guess she still
+wants to pretend she doesn't.</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3989,7 +3990,8 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>「Aaah… Onii-chan, not there, no—！  Nngh, nnggh… nngh！」</t>
+          <t>「Aaah… Onii-chan, not there, no—！  Nngh, nnggh…
+nngh！」</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -5336,8 +5338,8 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>Watching them, the conversation went on without really
-aligning.</t>
+          <t>Watching them, the conversation went on without
+really aligning.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5646,8 +5648,8 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>I leaned in and whispered softly to calm her down, and
-she responded with a string of small nods.</t>
+          <t>I leaned in and whispered softly to calm her down,
+and she responded with a string of small nods.</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5799,8 +5801,8 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>「I-I'm fine！ But if I'm more relaxed I'll be even more
-fine, so it's okay！」</t>
+          <t>「I-I'm fine！ But if I'm more relaxed I'll be even
+more fine, so it's okay！」</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5936,8 +5938,8 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>...When girls start talking to each other, it suddenly
-blossoms like a flower.</t>
+          <t>...When girls start talking to each other, it
+suddenly blossoms like a flower.</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6107,8 +6109,8 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>...No, no — in any case, given this situation, first I
-have to think about calming my penis down.</t>
+          <t>...No, no — in any case, given this situation, first
+I have to think about calming my penis down.</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -6123,8 +6125,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>I think being in the tub keeps me from getting caught,
-but this very posture is problematic.</t>
+          <t>I think being in the tub keeps me from getting
+caught, but this very posture is problematic.</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6475,9 +6477,9 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>There’s no way I can’t feel it with a penis inside me,
-but because I can’t make a sound, I tense up even more
-inwardly.</t>
+          <t>There’s no way I can’t feel it with a penis inside
+me, but because I can’t make a sound, I tense up even
+more inwardly.</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6725,9 +6727,9 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>Every time Miru-chan exhales, every time she bucks her
-hips, I can feel the walls of her vagina squelch and
-shift shape.</t>
+          <t>Every time Miru-chan exhales, every time she bucks
+her hips, I can feel the walls of her vagina squelch
+and shift shape.</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -7233,9 +7235,9 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>I was only scheming, but from Miru-chan's perspective,
-she probably doesn't like that I was looking at the
-others.</t>
+          <t>I was only scheming, but from Miru-chan's
+perspective, she probably doesn't like that I was
+looking at the others.</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7402,8 +7404,8 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help it, so with the spring of my knees and
-hips I thrust Miru-chan upward.</t>
+          <t>I couldn't help it, so with the spring of my knees
+and hips I thrust Miru-chan upward.</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7524,8 +7526,8 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>The moment she snapped back, her vaginal folds shifted
-noticeably.</t>
+          <t>The moment she snapped back, her vaginal folds
+shifted noticeably.</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7662,7 +7664,8 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>The wide, writhing vagina tightened rapidly this time.</t>
+          <t>The wide, writhing vagina tightened rapidly this
+time.</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7724,8 +7727,8 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Oh my, come to think of it you've been in the tub the
-whole time... aren't you getting lightheaded？」</t>
+          <t>「Oh my, come to think of it you've been in the tub
+the whole time... aren't you getting lightheaded？」</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7830,8 +7833,8 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>When I laugh and try to cover it up, Miru-chan puts on
-the same forced voice with me.</t>
+          <t>When I laugh and try to cover it up, Miru-chan puts
+on the same forced voice with me.</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -8077,8 +8080,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>Looking forward to getting in the tub... I feel like I
-said something I shouldn't have.</t>
+          <t>Looking forward to getting in the tub... I feel like
+I said something I shouldn't have.</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8093,8 +8096,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>But first she has to wash up, so anyway Rurichiyo-chan
-turned her back.</t>
+          <t>But first she has to wash up, so anyway
+Rurichiyo-chan turned her back.</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8492,7 +8495,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>「...Both of you, don't be rough in the bathtub, okay？」</t>
+          <t>「...Both of you, don't be rough in the bathtub,
+okay？」</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8894,8 +8898,8 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>Ah... I want to kiss her, I really want to slobber all
-over her mouth！</t>
+          <t>Ah... I want to kiss her, I really want to slobber
+all over her mouth！</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9428,8 +9432,9 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>As I fidget nervously thinking about what might happen
-next, Miru-chan smiled at me while breathing hard.</t>
+          <t>As I fidget nervously thinking about what might
+happen next, Miru-chan smiled at me while breathing
+hard.</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9611,8 +9616,8 @@
       </c>
       <c r="B597" s="1" t="inlineStr">
         <is>
-          <t>...At last, everyone finished washing their bodies and
-hair.</t>
+          <t>...At last, everyone finished washing their bodies
+and hair.</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -10122,8 +10127,8 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>When I think about it like that, I can't help but feel
-Miru-chan is growing up as a girl.</t>
+          <t>When I think about it like that, I can't help but
+feel Miru-chan is growing up as a girl.</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -10233,8 +10238,8 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>「Eh... ah, ahaha！ Yeah... Miru's already plenty warmed
-up, so I'll get out first, okay！」</t>
+          <t>「Eh... ah, ahaha！ Yeah... Miru's already plenty
+warmed up, so I'll get out first, okay！」</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10497,9 +10502,10 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>The water was white too, so everyone probably couldn't
-see into the tub, and unless they looked directly,
-they wouldn't even imagine what was happening.</t>
+          <t>The water was white too, so everyone probably
+couldn't see into the tub, and unless they looked
+directly, they wouldn't even imagine what was
+happening.</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10620,8 +10626,8 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>While I sorted out my thoughts and calmed my heart and
-head, everyone got into the bathtub chattering.</t>
+          <t>While I sorted out my thoughts and calmed my heart
+and head, everyone got into the bathtub chattering.</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -10727,8 +10733,8 @@
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>I secretly splashed the hot water, trying to drive the
-semen out of the bathtub.</t>
+          <t>I secretly splashed the hot water, trying to drive
+the semen out of the bathtub.</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -11060,8 +11066,8 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>When Rin-chan says this shyly, Nono-chan agrees with a
-wry smile.</t>
+          <t>When Rin-chan says this shyly, Nono-chan agrees with
+a wry smile.</t>
         </is>
       </c>
       <c r="C691" t="n">

--- a/processed_ruby_restored_xlsx/sc246_みるく８：牛乳風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc246_みるく８：牛乳風呂.ss.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan~, is the bath ready？」</t>
+          <t>Onii-chan~, is the bath ready？</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>「Geez, you mustn't run in the bath, okay？」</t>
+          <t>Geez, you mustn't run in the bath, okay？</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>「Then I'll put it in for you, Miru！」</t>
+          <t>Then I'll put it in for you, Miru！</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>「Mm, yeah. Thanks, then.」</t>
+          <t>Mm, yeah. Thanks, then.</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'm putting it in now！」</t>
+          <t>Okay, I'm putting it in now！</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>「...It's kind of light, isn't it？」</t>
+          <t>...It's kind of light, isn't it？</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1172,8 +1172,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>「That's because we haven't stirred it... hang on a
-sec.」</t>
+          <t>That's because we haven't stirred it... hang on a
+sec.</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>「...Still kind of light, huh？」</t>
+          <t>...Still kind of light, huh？</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>「This tub is big... maybe I'll add another one.」</t>
+          <t>This tub is big... maybe I'll add another one.</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>「Okay okay！ Then I'll put it in—！」</t>
+          <t>Okay okay！ Then I'll put it in—！</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>「Alright, go ahead.」</t>
+          <t>Alright, go ahead.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>「Fuhihi！ I'm putting it in~！」</t>
+          <t>Fuhihi！ I'm putting it in~！</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah—...」</t>
+          <t>Ah... ah—...</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1538,8 +1538,8 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>She's basically an honest kid, so the moment my tone
-drops, she picks up on it.</t>
+          <t>She's basically an honest kid, so she's敏感ly picking
+up the drop in my voice.</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2043,9 +2043,9 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>On that point, she figured that because the bathwater
-had gone cloudy, once she got in her embarrassment
-would be eased a bit.</t>
+          <t>On that point, they figured that because the
+bathwater had gone cloudy, once they got in their
+embarrassment would be eased a bit.</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>And because she's so straightforward, she tends to
+          <t>And because they're so straightforward, they tend to
 take wordplay at face value.</t>
         </is>
       </c>
@@ -2384,8 +2384,8 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>If you tease her at a time like that, you might end
-up making her angry.</t>
+          <t>If you tease them at a time like that, you might end
+up making them angry.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>「Nn... geez！ Nnngh...」</t>
+          <t>Nn... geez！ Nnngh...</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4007,7 +4007,7 @@
       <c r="B232" s="1" t="inlineStr">
         <is>
           <t>Miru-chan, saying it was no good, still kept jerking
-the penis back at me.</t>
+the penis back at him.</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn... Ehehe, Miru's the winner...？」</t>
+          <t>Nn, nnn... Ehehe, Miru's the winner...？</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4606,8 +4606,8 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>「Ah, Miruku-chan, you were already in here after all？
-Wait—Janitor-sensei！？」</t>
+          <t>Ah, Miruku-chan, you were already in here after all？
+Wait—Janitor-sensei！？</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>「M-My, so today we're all taking a bath together...？」</t>
+          <t>M-My, so today we're all taking a bath together...？</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5001,8 +5001,8 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>「Yes, today we were talking about everyone taking a
-bath together. Right, Nono-chan?」</t>
+          <t>Yes, today we were talking about everyone taking a
+bath together. Right, Nono-chan?</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5032,9 +5032,9 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>「Y-Yes！ Miruku-chan went to check if the bath was
+          <t>Y-Yes！ Miruku-chan went to check if the bath was
 ready, and she never came back, so we thought she
-might have gone in first...！」</t>
+might have gone in first...！</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>「But, to be in the bath with niini...!」</t>
+          <t>But, to be in the bath with niini...!</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>「I-It's not like that, okay？!」</t>
+          <t>I-It」s not like that, okay？!</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>「Well... I don't really care, though...」</t>
+          <t>Well... I don't really care, though...</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>「I-Is that okay？」</t>
+          <t>I-Is that okay？</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>「Well, I suppose that's fine...？」</t>
+          <t>Well, I suppose that's fine...？</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>「W-Well... if Rurichiyo-chan says so...」</t>
+          <t>W-Well... if Rurichiyo-chan says so...</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5386,8 +5386,8 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>「…A-And, well... as long as you don't do anything
-lewd, we'll let it slide！」</t>
+          <t>…A-And, well... as long as you don't do anything
+lewd, we'll let it slide！</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>Whenever Miru-chan moved, the folds of her pussy
+          <t>Whenever Miru-chan moved, the folds of my pussy
 heated and clenched around me...</t>
         </is>
       </c>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>It wasn't that Rin-chan had figured it out, but I
+          <t>It wasn't that Rin-chan had figured it out, but he
 probably became aware again that there were other
 girls around.</t>
         </is>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>「fah... ahh! ugh, ku... kuu, un...!」</t>
+          <t>fah... ahh! ugh, ku... kuu, un...!</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8448,8 +8448,8 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>Finally unable to hold back, I thrust my hips up
-sharply.</t>
+          <t>Finally unable to hold back, (he/she) thrust his/her
+hips up sharply.</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... sorry... but, just a little more！」</t>
+          <t>Ahaha... sorry... but, just a little more！</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -10393,8 +10393,8 @@
       </c>
       <c r="B647" s="1" t="inlineStr">
         <is>
-          <t>「Sigh... they were already in the bathtub by the time
-we got there.」</t>
+          <t>Sigh... they were already in the bathtub by the time
+we got there.</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -10990,8 +10990,8 @@
       </c>
       <c r="B686" s="1" t="inlineStr">
         <is>
-          <t>「...Rin-chan, you're being cold to Janitor-sensei,
-aren't you？」</t>
+          <t>...Rin-chan, you're being cold to Janitor-sensei,
+aren't you？</t>
         </is>
       </c>
       <c r="C686" t="n">
